--- a/src/test/resources/ExcelFile/ExcelData.xlsx
+++ b/src/test/resources/ExcelFile/ExcelData.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2448" windowWidth="17208" windowHeight="5196"/>
+    <workbookView xWindow="0" yWindow="2448" windowWidth="19200" windowHeight="5196" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:O16"/>
+  <oleSize ref="A1:Q15"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -446,7 +446,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
